--- a/experiment/HAT+CNN_bestx4/Test/results-Urban100/Urban100.xlsx
+++ b/experiment/HAT+CNN_bestx4/Test/results-Urban100/Urban100.xlsx
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.61</v>
+        <v>26.6</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8132</v>
+        <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.88</v>
+        <v>23.87</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6876</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.26</v>
+        <v>23.17</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8357</v>
+        <v>0.8341</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.8</v>
+        <v>27.79</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9493</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.52</v>
+        <v>22.51</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6267</v>
+        <v>0.6266</v>
       </c>
     </row>
     <row r="8">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.49</v>
+        <v>21.48</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6644</v>
+        <v>0.6646</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33.69</v>
+        <v>33.66</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9219000000000001</v>
+        <v>0.9213</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.05</v>
+        <v>27.02</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8841</v>
+        <v>0.8835</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.92</v>
+        <v>17.99</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7938</v>
+        <v>0.7949000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -598,7 +598,7 @@
         <v>23.85</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7319</v>
+        <v>0.7316</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.57</v>
+        <v>29.58</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8391</v>
+        <v>0.8396</v>
       </c>
     </row>
     <row r="15">
@@ -637,7 +637,7 @@
         <v>26.27</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7396</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.37</v>
+        <v>30.33</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9145</v>
+        <v>0.9139</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25.7</v>
+        <v>25.71</v>
       </c>
       <c r="C18" t="n">
-        <v>0.826</v>
+        <v>0.8264</v>
       </c>
     </row>
     <row r="19">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22.01</v>
+        <v>22</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8142</v>
+        <v>0.8139</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.12</v>
+        <v>22.13</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7175</v>
+        <v>0.7181999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -715,7 +715,7 @@
         <v>29.68</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7847</v>
+        <v>0.7846</v>
       </c>
     </row>
     <row r="23">
@@ -728,7 +728,7 @@
         <v>26.08</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7599</v>
+        <v>0.7596000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30.17</v>
+        <v>30.16</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9121</v>
+        <v>0.9117</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.93</v>
+        <v>19.85</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6526</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.03</v>
+        <v>31.92</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9018</v>
+        <v>0.9013</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.75</v>
+        <v>27.76</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7027</v>
+        <v>0.7022</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28.39</v>
+        <v>28.37</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7986</v>
+        <v>0.7977</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.42</v>
+        <v>31.46</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8781</v>
+        <v>0.8784</v>
       </c>
     </row>
     <row r="30">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27.32</v>
+        <v>27.31</v>
       </c>
       <c r="C30" t="n">
         <v>0.8719</v>
@@ -832,7 +832,7 @@
         <v>24.52</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8073</v>
+        <v>0.8076</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24.29</v>
+        <v>24.28</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7917</v>
+        <v>0.7917999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.34</v>
+        <v>29.33</v>
       </c>
       <c r="C33" t="n">
         <v>0.8609</v>
@@ -871,7 +871,7 @@
         <v>27.34</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8078</v>
+        <v>0.8080000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +884,7 @@
         <v>23.04</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5851</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.19</v>
+        <v>29.14</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.8791</v>
       </c>
     </row>
     <row r="37">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28.82</v>
+        <v>28.84</v>
       </c>
       <c r="C37" t="n">
         <v>0.8857</v>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26.49</v>
+        <v>26.5</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8014</v>
+        <v>0.8017</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>27.04</v>
+        <v>27.03</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6825</v>
+        <v>0.6822</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>22.96</v>
+        <v>22.97</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7389</v>
+        <v>0.7392</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27.2</v>
+        <v>27.12</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9405</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.27</v>
+        <v>26.32</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8833</v>
+        <v>0.8842</v>
       </c>
     </row>
     <row r="43">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32.39</v>
+        <v>32.27</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9361</v>
+        <v>0.9356</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.14</v>
+        <v>31.11</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8591</v>
+        <v>0.8582</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>23</v>
+        <v>22.86</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6637</v>
+        <v>0.6585</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23.61</v>
+        <v>23.62</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7573</v>
+        <v>0.7574</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7706</v>
+        <v>0.7713</v>
       </c>
     </row>
     <row r="49">
@@ -1066,7 +1066,7 @@
         <v>20.31</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8174</v>
+        <v>0.8169</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23.61</v>
+        <v>23.6</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.7541</v>
       </c>
     </row>
     <row r="51">
@@ -1092,7 +1092,7 @@
         <v>25.33</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7736</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>27.37</v>
+        <v>27.36</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8464</v>
+        <v>0.8466</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28.69</v>
+        <v>28.73</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9067</v>
+        <v>0.9074</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>22.34</v>
+        <v>22.32</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7274</v>
+        <v>0.7266</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>21.17</v>
+        <v>21.16</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6516</v>
+        <v>0.6514</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>33.15</v>
+        <v>33.12</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9449</v>
+        <v>0.9445</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24.95</v>
+        <v>24.93</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7819</v>
+        <v>0.7815</v>
       </c>
     </row>
     <row r="58">
@@ -1183,7 +1183,7 @@
         <v>31.04</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8972</v>
+        <v>0.8971</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25.78</v>
+        <v>25.77</v>
       </c>
       <c r="C59" t="n">
-        <v>0.857</v>
+        <v>0.8566</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>22.3</v>
+        <v>22.24</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7713</v>
+        <v>0.7698</v>
       </c>
     </row>
     <row r="61">
@@ -1222,7 +1222,7 @@
         <v>22.56</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5677</v>
+        <v>0.5678</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24.67</v>
+        <v>24.66</v>
       </c>
       <c r="C62" t="n">
-        <v>0.7551</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>21.79</v>
+        <v>21.77</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8134</v>
+        <v>0.8129</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22.32</v>
+        <v>22.34</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6199</v>
+        <v>0.6204</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>26.42</v>
+        <v>26.46</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7784</v>
+        <v>0.7796999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -1287,7 +1287,7 @@
         <v>25.33</v>
       </c>
       <c r="C66" t="n">
-        <v>0.7192</v>
+        <v>0.7191</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>22.15</v>
+        <v>22.16</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6383</v>
+        <v>0.6387</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>19.49</v>
+        <v>19.52</v>
       </c>
       <c r="C68" t="n">
-        <v>0.8791</v>
+        <v>0.8796</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>30.34</v>
+        <v>30.31</v>
       </c>
       <c r="C69" t="n">
-        <v>0.8848</v>
+        <v>0.8847</v>
       </c>
     </row>
     <row r="70">
@@ -1339,7 +1339,7 @@
         <v>24.73</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7518</v>
+        <v>0.7519</v>
       </c>
     </row>
     <row r="71">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>28.08</v>
+        <v>28.13</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6713</v>
+        <v>0.6732</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>19.98</v>
+        <v>20.02</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8171</v>
+        <v>0.8181</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>20.07</v>
+        <v>20.06</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5643</v>
+        <v>0.5647</v>
       </c>
     </row>
     <row r="75">
@@ -1404,7 +1404,7 @@
         <v>23.69</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7078</v>
+        <v>0.7062</v>
       </c>
     </row>
     <row r="76">
@@ -1417,7 +1417,7 @@
         <v>31.62</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8856000000000001</v>
+        <v>0.8855</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>23.01</v>
+        <v>22.93</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7367</v>
+        <v>0.7339</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>22.71</v>
+        <v>22.72</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6753</v>
+        <v>0.6751</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>27.41</v>
+        <v>27.37</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7738</v>
+        <v>0.7733</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>25.39</v>
+        <v>25.4</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.6954</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.51</v>
+        <v>35.45</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9523</v>
+        <v>0.9519</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>37.5</v>
+        <v>37.41</v>
       </c>
       <c r="C82" t="n">
-        <v>0.973</v>
+        <v>0.9728</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>32.91</v>
+        <v>32.92</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9413</v>
+        <v>0.9411</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.22</v>
+        <v>22.25</v>
       </c>
       <c r="C84" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.7022</v>
       </c>
     </row>
     <row r="85">
@@ -1534,7 +1534,7 @@
         <v>28.71</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8117</v>
+        <v>0.8116</v>
       </c>
     </row>
     <row r="86">
@@ -1547,7 +1547,7 @@
         <v>28.23</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9014</v>
+        <v>0.9016</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>30.21</v>
+        <v>30.25</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8847</v>
+        <v>0.8846000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.65</v>
+        <v>27.63</v>
       </c>
       <c r="C88" t="n">
-        <v>0.8824</v>
+        <v>0.8818</v>
       </c>
     </row>
     <row r="89">
@@ -1586,7 +1586,7 @@
         <v>19.83</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5694</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="90">
@@ -1599,7 +1599,7 @@
         <v>26.75</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7175</v>
+        <v>0.7176</v>
       </c>
     </row>
     <row r="91">
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>37.76</v>
+        <v>37.73</v>
       </c>
       <c r="C91" t="n">
         <v>0.9759</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>18.73</v>
+        <v>18.72</v>
       </c>
       <c r="C93" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.6479</v>
       </c>
     </row>
     <row r="94">
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>29.46</v>
+        <v>29.48</v>
       </c>
       <c r="C94" t="n">
         <v>0.9304</v>
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>27.14</v>
+        <v>27.13</v>
       </c>
       <c r="C95" t="n">
-        <v>0.783</v>
+        <v>0.7829</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20.17</v>
+        <v>20.18</v>
       </c>
       <c r="C96" t="n">
-        <v>0.447</v>
+        <v>0.4475</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>24.8</v>
+        <v>24.88</v>
       </c>
       <c r="C97" t="n">
-        <v>0.862</v>
+        <v>0.8641</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>24.86</v>
+        <v>24.84</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7618</v>
+        <v>0.7614</v>
       </c>
     </row>
     <row r="99">
@@ -1716,7 +1716,7 @@
         <v>20.71</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5345</v>
+        <v>0.5349</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>25.83</v>
+        <v>25.8</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7998</v>
+        <v>0.7993</v>
       </c>
     </row>
     <row r="101">
@@ -1742,7 +1742,7 @@
         <v>26.26</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7474</v>
+        <v>0.7477</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>25.99</v>
+        <v>25.98</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7834</v>
+        <v>0.7833</v>
       </c>
     </row>
   </sheetData>
